--- a/frågor_jeopardy_ny_omgång.xlsx
+++ b/frågor_jeopardy_ny_omgång.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Modern typ av hårddisk som kommer åt minnen snabbare än klassiska HDD</t>
+          <t>Modern typ av hårddisk som kommer åt data snabbare än klassiska HDD</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Historiens mest produktive matematiker som gav oss beteckningarna e och π samt arbetade vidare även som blind</t>
+          <t>Historiens mest produktive matematiker som gav oss beteckningen e, populariserade π och arbetade vidare även som blind</t>
         </is>
       </c>
     </row>

--- a/frågor_jeopardy_ny_omgång.xlsx
+++ b/frågor_jeopardy_ny_omgång.xlsx
@@ -1511,65 +1511,67 @@
     <row r="120">
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Om programledaren</t>
+          <t>Vem har dött?</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>sparven</t>
+          <t>Pippi Långstrump</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Djuret Jonas oftast förknippas med, vilket även är hans smeknamn</t>
+          <t>ljud-direkt</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Jakob och Hannes</t>
+          <t>Jocke Lundell</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Namnen på Jonas bröder</t>
+          <t>ljud-direkt</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Legorobotprogrammering</t>
+          <t>Carl von Linné</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Det Jonas vunnit VM i förutom minne</t>
+          <t>ljud-direkt</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>röd</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Jonas favoritfärg</t>
+          <t>ljud-direkt</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
-        <v>18</v>
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Justin Bieber</t>
+        </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Så många år har Jonas i oktober varit ihop med Jessica</t>
+          <t>ljud-direkt</t>
         </is>
       </c>
     </row>
